--- a/documentation/java/JavaFeaturesByVersion.xlsx
+++ b/documentation/java/JavaFeaturesByVersion.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/Documents - pushkarchauhan91’s MacBook Air/workspace_intellij/universal-dev-suite/documentation/java/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/workspaces/universal-dev-suite/documentation/java/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="4100" yWindow="2780" windowWidth="28760" windowHeight="17300" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="1820" windowWidth="28760" windowHeight="17300" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Java21" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>JEP : Java Enhancement Proposal</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -346,13 +342,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+  </cols>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/documentation/java/JavaFeaturesByVersion.xlsx
+++ b/documentation/java/JavaFeaturesByVersion.xlsx
@@ -5,14 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/workspaces/universal-dev-suite/documentation/java/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1820" windowWidth="28760" windowHeight="17300" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28760" windowHeight="17300" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Java21" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="150000" concurrentCalc="0"/>
   <extLst>
@@ -24,10 +24,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -342,9 +338,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-  </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
